--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0001T0006Z000C1N89_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0001T0006Z000C1N89_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>12.1795516567494</v>
+        <v>1.979177144221777</v>
       </c>
       <c r="D2" t="n">
-        <v>37.26127657663758</v>
+        <v>6.054957443703606</v>
       </c>
       <c r="E2" t="n">
-        <v>19.19485389009261</v>
+        <v>3.119163757140048</v>
       </c>
       <c r="F2" t="n">
-        <v>9.025951932169516</v>
+        <v>1.466717188977546</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>50.56925943693461</v>
+        <v>8.217504658501873</v>
       </c>
       <c r="D3" t="n">
-        <v>19.20937271229855</v>
+        <v>3.121523065748514</v>
       </c>
       <c r="E3" t="n">
-        <v>19.19485389009261</v>
+        <v>3.119163757140048</v>
       </c>
       <c r="F3" t="n">
-        <v>9.025951932169516</v>
+        <v>1.466717188977546</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
